--- a/technology_surveys/032_emerging_technology_integration_voting_form--technology_surveys.xlsx
+++ b/technology_surveys/032_emerging_technology_integration_voting_form--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,41 +520,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_1</t>
+          <t>intro_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Emerging Technology Integration</t>
+          <t>Please describe the current state of Emerging Technology in your organization.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_2</t>
+          <t>role_page</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Emerging Technology Integration</t>
+          <t>What is your role in the organization (e.g., developer, manager, user)?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_3</t>
+          <t>familiarity_page</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What are the key benefits of this emerging technology?</t>
+          <t>How familiar are you with Emerging Technology (on a scale of 1-10)?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_4</t>
+          <t>benefits_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What are some key use cases for this emerging technology?</t>
+          <t>What are the key benefits of Emerging Technology (e.g., automation, security, scalability)?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,85 +612,154 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_5</t>
+          <t>use_cases_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How important is this emerging technology for our business?</t>
+          <t>What are some key use cases for Emerging Technology (e.g., data analytics, AI, IoT)?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_6</t>
+          <t>importance_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emerging Technology Integration</t>
+          <t>How important is Emerging Technology for our business (on a scale of 1-10)?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_7</t>
+          <t>relevant_technology_page</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Emerging Technology Integration</t>
+          <t>Which Emerging Technology is the most relevant to our business (select one)?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_8</t>
+          <t>relevant_technologies_page</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Emerging Technology Integration</t>
+          <t>Which Emerging Technologies are most relevant to our business (select multiple)?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>adoption_date_page</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>What is the expected date of adoption for Emerging Technology in our organization?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>adoption_time_page</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>What time of day do you think Emerging Technology will be widely adopted in our organization?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>comments_page</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Do you have any additional comments or concerns regarding Emerging Technology?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -710,7 +779,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
@@ -735,7 +804,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_2_choices</t>
+          <t>relevant_technology_page_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -752,7 +821,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_2_choices</t>
+          <t>relevant_technology_page_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -769,7 +838,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_2_choices</t>
+          <t>relevant_technology_page_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -786,7 +855,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_6_choices</t>
+          <t>relevant_technologies_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -803,7 +872,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_6_choices</t>
+          <t>relevant_technologies_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -820,7 +889,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>emerging_technology_integration_voting_form_6_choices</t>
+          <t>relevant_technologies_page_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
